--- a/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,39; 71,24</t>
+          <t>65,2; 71,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,95; 79,65</t>
+          <t>74,0; 79,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,81; 76,05</t>
+          <t>69,87; 76,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,75; 66,75</t>
+          <t>58,43; 66,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,49; 82,88</t>
+          <t>78,5; 82,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,2; 88,92</t>
+          <t>85,22; 89,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,86; 88,12</t>
+          <t>83,53; 88,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,03; 73,22</t>
+          <t>67,95; 73,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,5; 77,16</t>
+          <t>73,57; 77,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,25; 84,45</t>
+          <t>81,26; 84,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78,61; 82,33</t>
+          <t>78,81; 82,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,22; 69,83</t>
+          <t>65,45; 70,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,18; 41,09</t>
+          <t>36,3; 40,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,91; 49,5</t>
+          <t>44,37; 49,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,7; 50,09</t>
+          <t>45,58; 50,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,61; 38,8</t>
+          <t>23,09; 38,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,46; 55,54</t>
+          <t>50,83; 55,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,95; 61,68</t>
+          <t>57,1; 61,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,78; 59,06</t>
+          <t>54,6; 59,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,22; 60,31</t>
+          <t>38,31; 58,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,74; 47,27</t>
+          <t>43,99; 47,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,19; 54,46</t>
+          <t>51,29; 54,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50,57; 53,86</t>
+          <t>50,63; 53,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,2; 47,92</t>
+          <t>33,36; 47,37</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,48; 44,12</t>
+          <t>35,36; 44,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,98; 52,89</t>
+          <t>42,28; 52,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,18; 44,66</t>
+          <t>36,56; 45,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,31; 37,31</t>
+          <t>29,14; 37,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,78; 57,09</t>
+          <t>48,06; 57,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,37; 59,18</t>
+          <t>49,41; 58,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,78; 52,39</t>
+          <t>43,77; 52,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,93; 38,49</t>
+          <t>32,06; 38,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,47; 48,99</t>
+          <t>42,46; 48,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,14; 54,28</t>
+          <t>47,58; 54,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,48; 47,44</t>
+          <t>41,63; 47,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,76; 36,74</t>
+          <t>31,67; 36,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,39; 50,01</t>
+          <t>46,41; 49,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,77; 57,26</t>
+          <t>53,99; 57,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,58; 54,08</t>
+          <t>50,58; 54,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,13; 41,81</t>
+          <t>29,91; 41,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,17; 65,77</t>
+          <t>62,3; 65,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,54; 70,62</t>
+          <t>67,68; 70,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,19; 65,5</t>
+          <t>62,07; 65,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,53; 57,99</t>
+          <t>44,58; 58,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,87; 57,41</t>
+          <t>54,92; 57,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,36; 63,7</t>
+          <t>61,34; 63,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,95; 59,37</t>
+          <t>57,04; 59,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,19; 48,57</t>
+          <t>39,18; 48,07</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>674598; 735003</t>
+          <t>672639; 736161</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>720714; 776282</t>
+          <t>721279; 774146</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>526578; 573696</t>
+          <t>527089; 574525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302522; 343714</t>
+          <t>300866; 342292</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1032201; 1090017</t>
+          <t>1032373; 1086684</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1139752; 1189559</t>
+          <t>1140014; 1193060</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>834131; 876524</t>
+          <t>830882; 877488</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>513968; 553175</t>
+          <t>513350; 552186</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1724960; 1810784</t>
+          <t>1726641; 1808969</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1878892; 1952856</t>
+          <t>1878986; 1950968</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1374830; 1440002</t>
+          <t>1378336; 1442960</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>828621; 887127</t>
+          <t>831568; 889887</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>612629; 695907</t>
+          <t>614636; 693508</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>881946; 972143</t>
+          <t>871317; 967589</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>948986; 1040134</t>
+          <t>946447; 1041298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>540707; 888741</t>
+          <t>528883; 886903</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>801185; 881829</t>
+          <t>806941; 885106</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1001041; 1084272</t>
+          <t>1003636; 1085979</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1089181; 1174234</t>
+          <t>1085609; 1175082</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>855221; 1349720</t>
+          <t>857418; 1308354</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1435019; 1551054</t>
+          <t>1443198; 1555069</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1905296; 2026697</t>
+          <t>1908929; 2028170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2055484; 2189397</t>
+          <t>2057925; 2189670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1548644; 2170077</t>
+          <t>1510795; 2144760</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>195629; 243273</t>
+          <t>194979; 244399</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>206797; 254504</t>
+          <t>203422; 252453</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197841; 244243</t>
+          <t>199960; 247993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189530; 241274</t>
+          <t>188410; 242143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>227649; 272003</t>
+          <t>228955; 272593</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>226430; 271411</t>
+          <t>226631; 270414</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>240414; 287675</t>
+          <t>240360; 288570</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>210882; 254233</t>
+          <t>211760; 255000</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>436523; 503557</t>
+          <t>436403; 501265</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>443065; 510119</t>
+          <t>447118; 508677</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>454589; 519956</t>
+          <t>456239; 520849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>415151; 480181</t>
+          <t>414016; 481227</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1519872; 1638673</t>
+          <t>1520616; 1636835</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1838857; 1958098</t>
+          <t>1846473; 1965979</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1708306; 1826709</t>
+          <t>1708287; 1825091</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1005639; 1443088</t>
+          <t>1032625; 1439462</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2100896; 2222608</t>
+          <t>2105314; 2214989</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2400426; 2509820</t>
+          <t>2405444; 2513092</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2196674; 2313531</t>
+          <t>2192331; 2309669</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1626972; 2118701</t>
+          <t>1628759; 2143139</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652324; 3821214</t>
+          <t>3655098; 3821684</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4279163; 4442682</t>
+          <t>4278122; 4439875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3935176; 4102585</t>
+          <t>3941042; 4103010</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2784440; 3451212</t>
+          <t>2783964; 3415469</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,2; 71,35</t>
+          <t>65,51; 71,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,0; 79,43</t>
+          <t>74,29; 79,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,87; 76,16</t>
+          <t>69,83; 76,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,43; 66,47</t>
+          <t>54,64; 63,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,5; 82,63</t>
+          <t>78,52; 82,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,22; 89,18</t>
+          <t>85,34; 89,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,53; 88,22</t>
+          <t>84,13; 88,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,95; 73,09</t>
+          <t>67,34; 72,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,57; 77,08</t>
+          <t>73,48; 77,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,26; 84,37</t>
+          <t>81,25; 84,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78,81; 82,5</t>
+          <t>78,46; 82,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,45; 70,05</t>
+          <t>63,13; 67,88</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,3; 40,95</t>
+          <t>36,23; 41,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,37; 49,27</t>
+          <t>44,87; 49,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,58; 50,15</t>
+          <t>45,81; 50,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 38,72</t>
+          <t>34,79; 39,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,83; 55,75</t>
+          <t>50,61; 55,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,1; 61,78</t>
+          <t>57,1; 61,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,6; 59,1</t>
+          <t>54,73; 59,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,31; 58,47</t>
+          <t>39,27; 43,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,99; 47,39</t>
+          <t>43,71; 47,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,29; 54,49</t>
+          <t>51,09; 54,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50,63; 53,87</t>
+          <t>50,56; 53,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,36; 47,37</t>
+          <t>37,35; 40,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,36; 44,32</t>
+          <t>35,45; 44,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,28; 52,47</t>
+          <t>42,77; 52,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,56; 45,35</t>
+          <t>36,58; 45,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,14; 37,45</t>
+          <t>29,22; 36,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,06; 57,22</t>
+          <t>47,06; 56,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,41; 58,96</t>
+          <t>48,85; 59,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,77; 52,55</t>
+          <t>44,15; 52,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,06; 38,61</t>
+          <t>31,96; 38,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,46; 48,77</t>
+          <t>42,16; 48,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,58; 54,13</t>
+          <t>47,83; 54,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,63; 47,52</t>
+          <t>41,47; 47,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,67; 36,82</t>
+          <t>31,33; 36,19</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,06%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,41; 49,96</t>
+          <t>46,5; 50,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,99; 57,49</t>
+          <t>53,93; 57,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,58; 54,03</t>
+          <t>50,57; 53,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,91; 41,7</t>
+          <t>37,78; 41,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,3; 65,55</t>
+          <t>62,11; 65,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,68; 70,71</t>
+          <t>67,5; 70,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,07; 65,39</t>
+          <t>62,1; 65,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,58; 58,66</t>
+          <t>44,82; 47,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,92; 57,42</t>
+          <t>54,84; 57,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,34; 63,66</t>
+          <t>61,25; 63,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,04; 59,38</t>
+          <t>57,02; 59,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,18; 48,07</t>
+          <t>41,86; 44,12</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>323514</t>
+          <t>340822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>534791</t>
+          <t>575451</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>858305</t>
+          <t>916273</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>672639; 736161</t>
+          <t>675933; 733782</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>721279; 774146</t>
+          <t>724095; 774300</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>527089; 574525</t>
+          <t>526790; 574833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300866; 342292</t>
+          <t>316096; 364800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1032373; 1086684</t>
+          <t>1032605; 1090816</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1140014; 1193060</t>
+          <t>1141669; 1191425</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>830882; 877488</t>
+          <t>836854; 877595</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>513350; 552186</t>
+          <t>553527; 596771</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1726641; 1808969</t>
+          <t>1724435; 1810431</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1878986; 1950968</t>
+          <t>1878839; 1953188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1378336; 1442960</t>
+          <t>1372211; 1440187</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>831568; 889887</t>
+          <t>884119; 950731</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>778251</t>
+          <t>822434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1008486</t>
+          <t>892405</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1786737</t>
+          <t>1714839</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>614636; 693508</t>
+          <t>613515; 695593</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>871317; 967589</t>
+          <t>881174; 970629</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>946447; 1041298</t>
+          <t>951141; 1042091</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>528883; 886903</t>
+          <t>776031; 874903</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>806941; 885106</t>
+          <t>803574; 882485</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1003636; 1085979</t>
+          <t>1003774; 1087819</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1085609; 1175082</t>
+          <t>1088161; 1177220</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>857418; 1308354</t>
+          <t>852676; 938616</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1443198; 1555069</t>
+          <t>1434097; 1552441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1908929; 2028170</t>
+          <t>1901469; 2024392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2057925; 2189670</t>
+          <t>2055086; 2187455</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1510795; 2144760</t>
+          <t>1644131; 1782485</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215109</t>
+          <t>232604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>232462</t>
+          <t>257703</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>447571</t>
+          <t>490307</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>194979; 244399</t>
+          <t>195480; 243350</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>203422; 252453</t>
+          <t>205795; 252794</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>199960; 247993</t>
+          <t>200033; 247353</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>188410; 242143</t>
+          <t>207906; 260591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>228955; 272593</t>
+          <t>224195; 270543</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>226631; 270414</t>
+          <t>224038; 270595</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>240360; 288570</t>
+          <t>242462; 289110</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>211760; 255000</t>
+          <t>234856; 279988</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>436403; 501265</t>
+          <t>433342; 500243</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>447118; 508677</t>
+          <t>449535; 511145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>456239; 520849</t>
+          <t>454533; 523741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>414016; 481227</t>
+          <t>453131; 523410</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1316875</t>
+          <t>1395860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1775739</t>
+          <t>1725559</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3092614</t>
+          <t>3121419</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1520616; 1636835</t>
+          <t>1523547; 1639290</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1846473; 1965979</t>
+          <t>1844369; 1962355</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1708287; 1825091</t>
+          <t>1708050; 1822984</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1032625; 1439462</t>
+          <t>1330011; 1455377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2105314; 2214989</t>
+          <t>2098769; 2211245</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2405444; 2513092</t>
+          <t>2399140; 2515721</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2192331; 2309669</t>
+          <t>2193422; 2316451</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1628759; 2143139</t>
+          <t>1670900; 1777207</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3655098; 3821684</t>
+          <t>3649928; 3815091</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4278122; 4439875</t>
+          <t>4271366; 4440036</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3941042; 4103010</t>
+          <t>3939676; 4101987</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2783964; 3415469</t>
+          <t>3034307; 3198032</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
